--- a/docs/verification/files/geostudio/gs2_rdd_slow.xlsx
+++ b/docs/verification/files/geostudio/gs2_rdd_slow.xlsx
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="480" uniqueCount="266">
   <si>
     <t>X</t>
   </si>
@@ -1023,6 +1023,9 @@
   </si>
   <si>
     <t>save_times</t>
+  </si>
+  <si>
+    <t>reservoir</t>
   </si>
 </sst>
 </file>
@@ -13710,7 +13713,7 @@
       <c r="C3" s="62"/>
       <c r="E3" s="32" t="inlineStr">
         <is>
-          <t>head</t>
+          <t>reservoir</t>
         </is>
       </c>
       <c r="F3" s="33" t="inlineStr">
@@ -13835,7 +13838,9 @@
       <c r="O6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
-      <c r="T6" s="1"/>
+      <c r="T6" s="1" t="s">
+        <v>265</v>
+      </c>
       <c r="U6" s="9"/>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
@@ -14117,7 +14122,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{21F200C9-4829-4345-9958-0F754F272AD0}">
-      <formula1>$T$4:$T$5</formula1>
+      <formula1>$T$4:$T$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14267,6 +14272,9 @@
       <c r="O6" s="3"/>
       <c r="Q6" s="3"/>
       <c r="R6" s="3"/>
+      <c r="T6" s="1" t="s">
+        <v>265</v>
+      </c>
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="3"/>
@@ -14531,7 +14539,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E3 H3 K3 N3 Q3" xr:uid="{68C61D93-1721-F843-8E53-0F0E50006C65}">
-      <formula1>$T$4:$T$5</formula1>
+      <formula1>$T$4:$T$6</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/verification/files/geostudio/gs2_rdd_slow.xlsx
+++ b/docs/verification/files/geostudio/gs2_rdd_slow.xlsx
@@ -5701,13 +5701,13 @@
         <v>0.0</v>
       </c>
       <c r="AA11" s="3">
-        <v>1.2</v>
+        <v>0.0</v>
       </c>
       <c r="AB11" s="3">
-        <v>1.8</v>
+        <v>0.0</v>
       </c>
       <c r="AC11" s="3">
-        <v>2.744</v>
+        <v>0.0</v>
       </c>
       <c r="AD11" s="3">
         <v>0.0</v>
@@ -5831,13 +5831,13 @@
         <v>0.0</v>
       </c>
       <c r="AA12" s="3">
-        <v>1.2</v>
+        <v>0.0</v>
       </c>
       <c r="AB12" s="3">
-        <v>1.8</v>
+        <v>0.0</v>
       </c>
       <c r="AC12" s="3">
-        <v>2.744</v>
+        <v>0.0</v>
       </c>
       <c r="AD12" s="3">
         <v>0.0</v>
